--- a/WebRoot/oem/dacheng/locale/locale-en.xlsx
+++ b/WebRoot/oem/dacheng/locale/locale-en.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0A30E1-B4ED-491A-8C6C-C5BE550599BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A8C095-8374-465D-968B-5CBAED1BB60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="732" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="732" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="video" sheetId="10" r:id="rId10"/>
     <sheet name="protocol" sheetId="12" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5985" uniqueCount="4602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5993" uniqueCount="4608">
   <si>
     <t>myself</t>
   </si>
@@ -17087,6 +17087,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>applicationScenarios2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水文观测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hydrological observations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>大城煤层气生产数据采集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -17100,6 +17112,18 @@
   </si>
   <si>
     <t>The "Dacheng Coalbed Methane Production Data Collection" mainly includes real-time monitoring, historical query, production report, alarm query, equipment log, system log, data maintenance, drive configuration, permission management, equipment management, system configuration and other modules to realize the collection and control of coalbed methane well data. Provide data decision-making support for stable production, efficiency enhancement and safe operation of coalbed methane production.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numericCalculation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值运算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Numerical operations</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17192,7 +17216,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -17214,6 +17238,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -17269,7 +17299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -17346,6 +17376,9 @@
     <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -20424,14 +20457,14 @@
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="48" t="s">
-        <v>4598</v>
+      <c r="C2" s="49" t="s">
+        <v>4601</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4599</v>
+        <v>4602</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>4599</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -20441,14 +20474,14 @@
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="48" t="s">
-        <v>4600</v>
+      <c r="C3" s="49" t="s">
+        <v>4603</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4601</v>
+        <v>4604</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>4601</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -20458,9 +20491,9 @@
       <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11">
@@ -26803,7 +26836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41FBAC76-7507-496A-9947-9F636F0BCBC6}">
-  <dimension ref="A1:E783"/>
+  <dimension ref="A1:E785"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="42.6640625" customWidth="1"/>
@@ -37047,20 +37080,20 @@
       </c>
     </row>
     <row r="603" spans="1:5">
-      <c r="A603" s="11">
+      <c r="A603" s="48">
         <v>602</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C603" s="13" t="s">
-        <v>1674</v>
-      </c>
-      <c r="D603" s="20" t="s">
-        <v>3003</v>
-      </c>
-      <c r="E603" s="24" t="s">
-        <v>3003</v>
+        <v>4598</v>
+      </c>
+      <c r="C603" s="42" t="s">
+        <v>4599</v>
+      </c>
+      <c r="D603" s="43" t="s">
+        <v>4600</v>
+      </c>
+      <c r="E603" s="45" t="s">
+        <v>4600</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -37068,16 +37101,16 @@
         <v>603</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C604" s="13" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="D604" s="20" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E604" s="24" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -37085,16 +37118,16 @@
         <v>604</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C605" s="13" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="D605" s="20" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="E605" s="24" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -37102,16 +37135,16 @@
         <v>605</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C606" s="13" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="D606" s="20" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="E606" s="24" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -37119,16 +37152,16 @@
         <v>606</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C607" s="13" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="D607" s="20" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="E607" s="24" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="608" spans="1:5">
@@ -37136,16 +37169,16 @@
         <v>607</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>886</v>
+        <v>865</v>
       </c>
       <c r="C608" s="13" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="D608" s="20" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="E608" s="24" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -37153,16 +37186,16 @@
         <v>608</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C609" s="13" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D609" s="20" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="E609" s="24" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -37170,16 +37203,16 @@
         <v>609</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C610" s="13" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="D610" s="20" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="E610" s="24" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="611" spans="1:5">
@@ -37187,16 +37220,16 @@
         <v>610</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C611" s="13" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D611" s="20" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="E611" s="24" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="612" spans="1:5">
@@ -37204,16 +37237,16 @@
         <v>611</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C612" s="13" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D612" s="20" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="E612" s="24" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -37221,16 +37254,16 @@
         <v>612</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C613" s="13" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D613" s="20" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="E613" s="24" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="614" spans="1:5">
@@ -37238,16 +37271,16 @@
         <v>613</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C614" s="13" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D614" s="20" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="E614" s="24" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -37255,16 +37288,16 @@
         <v>614</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C615" s="13" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D615" s="20" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="E615" s="24" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -37272,16 +37305,16 @@
         <v>615</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C616" s="13" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="D616" s="20" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="E616" s="24" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -37289,16 +37322,16 @@
         <v>616</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="C617" s="13" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="D617" s="20" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="E617" s="24" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -37306,16 +37339,16 @@
         <v>617</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C618" s="13" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D618" s="20" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E618" s="24" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -37323,16 +37356,16 @@
         <v>618</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C619" s="13" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D619" s="20" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="E619" s="24" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -37340,16 +37373,16 @@
         <v>619</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C620" s="13" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D620" s="20" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="E620" s="24" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -37357,16 +37390,16 @@
         <v>620</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C621" s="13" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="D621" s="20" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="E621" s="24" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -37374,16 +37407,16 @@
         <v>621</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="C622" s="13" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="D622" s="20" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="E622" s="24" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -37391,16 +37424,16 @@
         <v>622</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C623" s="13" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D623" s="20" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="E623" s="24" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -37408,16 +37441,16 @@
         <v>623</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C624" s="13" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="D624" s="20" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="E624" s="24" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -37425,16 +37458,16 @@
         <v>624</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C625" s="13" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D625" s="20" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="E625" s="24" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -37442,16 +37475,16 @@
         <v>625</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C626" s="13" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D626" s="20" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="E626" s="24" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -37459,16 +37492,16 @@
         <v>626</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C627" s="13" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="D627" s="20" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="E627" s="24" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -37476,16 +37509,16 @@
         <v>627</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C628" s="13" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="D628" s="20" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="E628" s="24" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -37493,33 +37526,33 @@
         <v>628</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C629" s="13" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="D629" s="20" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="E629" s="24" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="630" spans="1:5">
       <c r="A630" s="11">
         <v>629</v>
       </c>
-      <c r="B630" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C630" s="42" t="s">
-        <v>1701</v>
-      </c>
-      <c r="D630" s="43" t="s">
-        <v>3030</v>
-      </c>
-      <c r="E630" s="45" t="s">
-        <v>3030</v>
+      <c r="B630" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C630" s="13" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D630" s="20" t="s">
+        <v>3029</v>
+      </c>
+      <c r="E630" s="24" t="s">
+        <v>3029</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -37527,16 +37560,16 @@
         <v>630</v>
       </c>
       <c r="B631" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C631" s="42" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D631" s="43" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="E631" s="45" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -37544,33 +37577,33 @@
         <v>631</v>
       </c>
       <c r="B632" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C632" s="13" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D632" s="20" t="s">
-        <v>3032</v>
-      </c>
-      <c r="E632" s="24" t="s">
-        <v>3032</v>
+        <v>915</v>
+      </c>
+      <c r="C632" s="42" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D632" s="43" t="s">
+        <v>3031</v>
+      </c>
+      <c r="E632" s="45" t="s">
+        <v>3031</v>
       </c>
     </row>
     <row r="633" spans="1:5">
       <c r="A633" s="11">
         <v>632</v>
       </c>
-      <c r="B633" s="3" t="s">
-        <v>917</v>
+      <c r="B633" s="4" t="s">
+        <v>916</v>
       </c>
       <c r="C633" s="13" t="s">
-        <v>3085</v>
+        <v>1703</v>
       </c>
       <c r="D633" s="20" t="s">
-        <v>3086</v>
+        <v>3032</v>
       </c>
       <c r="E633" s="24" t="s">
-        <v>3086</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -37578,16 +37611,16 @@
         <v>633</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>1073</v>
+        <v>917</v>
       </c>
       <c r="C634" s="13" t="s">
-        <v>1704</v>
+        <v>3085</v>
       </c>
       <c r="D634" s="20" t="s">
-        <v>3033</v>
+        <v>3086</v>
       </c>
       <c r="E634" s="24" t="s">
-        <v>3033</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -37595,16 +37628,16 @@
         <v>634</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="C635" s="13" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D635" s="20" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="E635" s="24" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -37612,16 +37645,16 @@
         <v>635</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C636" s="13" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D636" s="20" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="E636" s="24" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -37629,16 +37662,16 @@
         <v>636</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C637" s="13" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D637" s="20" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="E637" s="24" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -37646,16 +37679,16 @@
         <v>637</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C638" s="13" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D638" s="20" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="E638" s="24" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -37663,16 +37696,16 @@
         <v>638</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C639" s="13" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D639" s="20" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="E639" s="24" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -37680,16 +37713,16 @@
         <v>639</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C640" s="13" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="D640" s="20" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="E640" s="24" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -37697,16 +37730,16 @@
         <v>640</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C641" s="13" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="D641" s="20" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="E641" s="24" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -37714,16 +37747,16 @@
         <v>641</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C642" s="13" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D642" s="20" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="E642" s="24" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="643" spans="1:5">
@@ -37731,16 +37764,16 @@
         <v>642</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C643" s="13" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D643" s="20" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="E643" s="24" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -37748,16 +37781,16 @@
         <v>643</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C644" s="13" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D644" s="20" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="E644" s="24" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="645" spans="1:5">
@@ -37765,50 +37798,50 @@
         <v>644</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C645" s="13" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D645" s="20" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="E645" s="24" t="s">
-        <v>3044</v>
-      </c>
-    </row>
-    <row r="646" spans="1:5" ht="15">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5">
       <c r="A646" s="11">
         <v>645</v>
       </c>
-      <c r="B646" s="17" t="s">
-        <v>3339</v>
+      <c r="B646" s="3" t="s">
+        <v>1085</v>
       </c>
       <c r="C646" s="13" t="s">
-        <v>3303</v>
+        <v>1715</v>
       </c>
       <c r="D646" s="20" t="s">
-        <v>3304</v>
+        <v>3044</v>
       </c>
       <c r="E646" s="24" t="s">
-        <v>3304</v>
-      </c>
-    </row>
-    <row r="647" spans="1:5">
+        <v>3044</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" ht="15">
       <c r="A647" s="11">
         <v>646</v>
       </c>
-      <c r="B647" s="1" t="s">
-        <v>3340</v>
+      <c r="B647" s="17" t="s">
+        <v>3339</v>
       </c>
       <c r="C647" s="13" t="s">
-        <v>3305</v>
+        <v>3303</v>
       </c>
       <c r="D647" s="20" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="E647" s="24" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -37816,16 +37849,16 @@
         <v>647</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>3310</v>
+        <v>3340</v>
       </c>
       <c r="C648" s="13" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="D648" s="20" t="s">
-        <v>3310</v>
+        <v>3306</v>
       </c>
       <c r="E648" s="24" t="s">
-        <v>3310</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="649" spans="1:5">
@@ -37833,16 +37866,16 @@
         <v>648</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="C649" s="13" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="D649" s="20" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="E649" s="24" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -37850,16 +37883,16 @@
         <v>649</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>3314</v>
-      </c>
-      <c r="C650" s="14" t="s">
-        <v>3311</v>
+        <v>3309</v>
+      </c>
+      <c r="C650" s="13" t="s">
+        <v>3308</v>
       </c>
       <c r="D650" s="20" t="s">
-        <v>3314</v>
+        <v>3309</v>
       </c>
       <c r="E650" s="24" t="s">
-        <v>3314</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -37867,16 +37900,16 @@
         <v>650</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="C651" s="14" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="D651" s="20" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="E651" s="24" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="652" spans="1:5">
@@ -37884,16 +37917,16 @@
         <v>651</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="C652" s="14" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="D652" s="20" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="E652" s="24" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -37901,16 +37934,16 @@
         <v>652</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>3338</v>
+        <v>3316</v>
       </c>
       <c r="C653" s="14" t="s">
-        <v>3337</v>
+        <v>3313</v>
       </c>
       <c r="D653" s="20" t="s">
-        <v>3338</v>
+        <v>3316</v>
       </c>
       <c r="E653" s="24" t="s">
-        <v>3338</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -37918,16 +37951,16 @@
         <v>653</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>3341</v>
+        <v>3338</v>
       </c>
       <c r="C654" s="14" t="s">
-        <v>3319</v>
+        <v>3337</v>
       </c>
       <c r="D654" s="20" t="s">
-        <v>3320</v>
+        <v>3338</v>
       </c>
       <c r="E654" s="24" t="s">
-        <v>3320</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -37935,16 +37968,16 @@
         <v>654</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="C655" s="14" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="D655" s="20" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
       <c r="E655" s="24" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="656" spans="1:5">
@@ -37952,16 +37985,16 @@
         <v>655</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="C656" s="14" t="s">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="D656" s="20" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
       <c r="E656" s="24" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -37969,16 +38002,16 @@
         <v>656</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="C657" s="14" t="s">
-        <v>3325</v>
+        <v>3323</v>
       </c>
       <c r="D657" s="20" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
       <c r="E657" s="24" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -37986,16 +38019,16 @@
         <v>657</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>3328</v>
-      </c>
-      <c r="C658" s="13" t="s">
-        <v>3327</v>
+        <v>3344</v>
+      </c>
+      <c r="C658" s="14" t="s">
+        <v>3325</v>
       </c>
       <c r="D658" s="20" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
       <c r="E658" s="24" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -38003,16 +38036,16 @@
         <v>658</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>3345</v>
-      </c>
-      <c r="C659" s="14" t="s">
-        <v>3329</v>
+        <v>3328</v>
+      </c>
+      <c r="C659" s="13" t="s">
+        <v>3327</v>
       </c>
       <c r="D659" s="20" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="E659" s="24" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -38020,16 +38053,16 @@
         <v>659</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="C660" s="14" t="s">
-        <v>3331</v>
+        <v>3329</v>
       </c>
       <c r="D660" s="20" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
       <c r="E660" s="24" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -38037,16 +38070,16 @@
         <v>660</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="C661" s="14" t="s">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="D661" s="20" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
       <c r="E661" s="24" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -38054,33 +38087,33 @@
         <v>661</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="C662" s="14" t="s">
-        <v>3335</v>
+        <v>3333</v>
       </c>
       <c r="D662" s="20" t="s">
-        <v>3336</v>
+        <v>3334</v>
       </c>
       <c r="E662" s="24" t="s">
-        <v>3336</v>
+        <v>3334</v>
       </c>
     </row>
     <row r="663" spans="1:5">
       <c r="A663" s="11">
         <v>662</v>
       </c>
-      <c r="B663" s="3" t="s">
-        <v>3350</v>
-      </c>
-      <c r="C663" s="13" t="s">
-        <v>3351</v>
+      <c r="B663" s="1" t="s">
+        <v>3348</v>
+      </c>
+      <c r="C663" s="14" t="s">
+        <v>3335</v>
       </c>
       <c r="D663" s="20" t="s">
-        <v>480</v>
+        <v>3336</v>
       </c>
       <c r="E663" s="24" t="s">
-        <v>480</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -38088,16 +38121,16 @@
         <v>663</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>3352</v>
+        <v>3350</v>
       </c>
       <c r="C664" s="13" t="s">
-        <v>3353</v>
+        <v>3351</v>
       </c>
       <c r="D664" s="20" t="s">
-        <v>3354</v>
+        <v>480</v>
       </c>
       <c r="E664" s="24" t="s">
-        <v>3354</v>
+        <v>480</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -38105,16 +38138,16 @@
         <v>664</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>3358</v>
+        <v>3352</v>
       </c>
       <c r="C665" s="13" t="s">
-        <v>3359</v>
+        <v>3353</v>
       </c>
       <c r="D665" s="20" t="s">
-        <v>3360</v>
+        <v>3354</v>
       </c>
       <c r="E665" s="24" t="s">
-        <v>3360</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -38122,16 +38155,16 @@
         <v>665</v>
       </c>
       <c r="B666" s="3" t="s">
-        <v>3630</v>
+        <v>3358</v>
       </c>
       <c r="C666" s="13" t="s">
-        <v>3628</v>
+        <v>3359</v>
       </c>
       <c r="D666" s="20" t="s">
-        <v>3629</v>
+        <v>3360</v>
       </c>
       <c r="E666" s="24" t="s">
-        <v>3629</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -38139,16 +38172,16 @@
         <v>666</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>3641</v>
+        <v>3630</v>
       </c>
       <c r="C667" s="13" t="s">
-        <v>3640</v>
+        <v>3628</v>
       </c>
       <c r="D667" s="20" t="s">
-        <v>837</v>
+        <v>3629</v>
       </c>
       <c r="E667" s="24" t="s">
-        <v>837</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -38156,16 +38189,16 @@
         <v>667</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>3645</v>
+        <v>3641</v>
       </c>
       <c r="C668" s="13" t="s">
-        <v>3646</v>
+        <v>3640</v>
       </c>
       <c r="D668" s="20" t="s">
-        <v>3647</v>
+        <v>837</v>
       </c>
       <c r="E668" s="24" t="s">
-        <v>3647</v>
+        <v>837</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -38173,16 +38206,16 @@
         <v>668</v>
       </c>
       <c r="B669" s="3" t="s">
-        <v>3650</v>
+        <v>3645</v>
       </c>
       <c r="C669" s="13" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="D669" s="20" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="E669" s="24" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -38190,16 +38223,16 @@
         <v>669</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>3655</v>
+        <v>3650</v>
       </c>
       <c r="C670" s="13" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
       <c r="D670" s="20" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="E670" s="24" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -38207,16 +38240,16 @@
         <v>670</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>3668</v>
+        <v>3655</v>
       </c>
       <c r="C671" s="13" t="s">
-        <v>3669</v>
+        <v>3653</v>
       </c>
       <c r="D671" s="20" t="s">
-        <v>3670</v>
+        <v>3654</v>
       </c>
       <c r="E671" s="24" t="s">
-        <v>3670</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -38224,16 +38257,16 @@
         <v>671</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>3679</v>
+        <v>3668</v>
       </c>
       <c r="C672" s="13" t="s">
-        <v>3681</v>
+        <v>3669</v>
       </c>
       <c r="D672" s="20" t="s">
-        <v>3682</v>
+        <v>3670</v>
       </c>
       <c r="E672" s="24" t="s">
-        <v>3682</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -38241,16 +38274,16 @@
         <v>672</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="C673" s="13" t="s">
-        <v>3683</v>
+        <v>3681</v>
       </c>
       <c r="D673" s="20" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="E673" s="24" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="674" spans="1:5">
@@ -38258,16 +38291,16 @@
         <v>673</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>3685</v>
+        <v>3680</v>
       </c>
       <c r="C674" s="13" t="s">
-        <v>3686</v>
+        <v>3683</v>
       </c>
       <c r="D674" s="20" t="s">
-        <v>3691</v>
+        <v>3684</v>
       </c>
       <c r="E674" s="24" t="s">
-        <v>3691</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -38275,16 +38308,16 @@
         <v>674</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
       <c r="C675" s="13" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="D675" s="20" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="E675" s="24" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="676" spans="1:5">
@@ -38292,16 +38325,16 @@
         <v>675</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
       <c r="C676" s="13" t="s">
-        <v>3690</v>
+        <v>3688</v>
       </c>
       <c r="D676" s="20" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
       <c r="E676" s="24" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="677" spans="1:5">
@@ -38309,16 +38342,16 @@
         <v>676</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>3694</v>
+        <v>3689</v>
       </c>
       <c r="C677" s="13" t="s">
-        <v>3695</v>
+        <v>3690</v>
       </c>
       <c r="D677" s="20" t="s">
-        <v>3696</v>
+        <v>3693</v>
       </c>
       <c r="E677" s="24" t="s">
-        <v>3696</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="678" spans="1:5">
@@ -38326,16 +38359,16 @@
         <v>677</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>3697</v>
+        <v>3694</v>
       </c>
       <c r="C678" s="13" t="s">
-        <v>3698</v>
+        <v>3695</v>
       </c>
       <c r="D678" s="20" t="s">
-        <v>3699</v>
+        <v>3696</v>
       </c>
       <c r="E678" s="24" t="s">
-        <v>3699</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="679" spans="1:5">
@@ -38343,16 +38376,16 @@
         <v>678</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>3700</v>
+        <v>3697</v>
       </c>
       <c r="C679" s="13" t="s">
-        <v>3701</v>
+        <v>3698</v>
       </c>
       <c r="D679" s="20" t="s">
-        <v>3702</v>
+        <v>3699</v>
       </c>
       <c r="E679" s="24" t="s">
-        <v>3702</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -38360,16 +38393,16 @@
         <v>679</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>3703</v>
+        <v>3700</v>
       </c>
       <c r="C680" s="13" t="s">
-        <v>3704</v>
+        <v>3701</v>
       </c>
       <c r="D680" s="20" t="s">
-        <v>3705</v>
+        <v>3702</v>
       </c>
       <c r="E680" s="24" t="s">
-        <v>3705</v>
+        <v>3702</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -38377,16 +38410,16 @@
         <v>680</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>3706</v>
+        <v>3703</v>
       </c>
       <c r="C681" s="13" t="s">
-        <v>3707</v>
+        <v>3704</v>
       </c>
       <c r="D681" s="20" t="s">
-        <v>3708</v>
+        <v>3705</v>
       </c>
       <c r="E681" s="24" t="s">
-        <v>3708</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -38394,16 +38427,16 @@
         <v>681</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>3712</v>
+        <v>3706</v>
       </c>
       <c r="C682" s="13" t="s">
-        <v>3713</v>
+        <v>3707</v>
       </c>
       <c r="D682" s="20" t="s">
-        <v>3714</v>
+        <v>3708</v>
       </c>
       <c r="E682" s="24" t="s">
-        <v>3714</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="683" spans="1:5">
@@ -38411,16 +38444,16 @@
         <v>682</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>3715</v>
+        <v>3712</v>
       </c>
       <c r="C683" s="13" t="s">
-        <v>3716</v>
+        <v>3713</v>
       </c>
       <c r="D683" s="20" t="s">
-        <v>3717</v>
+        <v>3714</v>
       </c>
       <c r="E683" s="24" t="s">
-        <v>3717</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="684" spans="1:5">
@@ -38428,16 +38461,16 @@
         <v>683</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>3720</v>
+        <v>3715</v>
       </c>
       <c r="C684" s="13" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="D684" s="20" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
       <c r="E684" s="24" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="685" spans="1:5">
@@ -38445,16 +38478,16 @@
         <v>684</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="C685" s="13" t="s">
-        <v>3722</v>
+        <v>3718</v>
       </c>
       <c r="D685" s="20" t="s">
-        <v>3729</v>
+        <v>3719</v>
       </c>
       <c r="E685" s="24" t="s">
-        <v>3729</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -38462,16 +38495,16 @@
         <v>685</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>3723</v>
+        <v>3721</v>
       </c>
       <c r="C686" s="13" t="s">
-        <v>3724</v>
+        <v>3722</v>
       </c>
       <c r="D686" s="20" t="s">
-        <v>3730</v>
+        <v>3729</v>
       </c>
       <c r="E686" s="24" t="s">
-        <v>3730</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="687" spans="1:5">
@@ -38479,16 +38512,16 @@
         <v>686</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>3725</v>
+        <v>3723</v>
       </c>
       <c r="C687" s="13" t="s">
-        <v>3726</v>
+        <v>3724</v>
       </c>
       <c r="D687" s="20" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="E687" s="24" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="688" spans="1:5">
@@ -38496,16 +38529,16 @@
         <v>687</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="C688" s="13" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="D688" s="20" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="E688" s="24" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -38513,16 +38546,16 @@
         <v>688</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>3876</v>
+        <v>3727</v>
       </c>
       <c r="C689" s="13" t="s">
-        <v>3867</v>
+        <v>3728</v>
       </c>
       <c r="D689" s="20" t="s">
-        <v>3866</v>
+        <v>3732</v>
       </c>
       <c r="E689" s="24" t="s">
-        <v>3866</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="690" spans="1:5">
@@ -38530,16 +38563,16 @@
         <v>689</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>3736</v>
+        <v>3876</v>
       </c>
       <c r="C690" s="13" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="D690" s="20" t="s">
-        <v>3869</v>
+        <v>3866</v>
       </c>
       <c r="E690" s="24" t="s">
-        <v>3869</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -38547,16 +38580,16 @@
         <v>690</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="C691" s="13" t="s">
-        <v>3738</v>
+        <v>3868</v>
       </c>
       <c r="D691" s="20" t="s">
-        <v>3799</v>
+        <v>3869</v>
       </c>
       <c r="E691" s="24" t="s">
-        <v>3799</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="692" spans="1:5">
@@ -38564,16 +38597,16 @@
         <v>691</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>3739</v>
+        <v>3737</v>
       </c>
       <c r="C692" s="13" t="s">
-        <v>3740</v>
+        <v>3738</v>
       </c>
       <c r="D692" s="20" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="E692" s="24" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="693" spans="1:5">
@@ -38581,16 +38614,16 @@
         <v>692</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>3741</v>
+        <v>3739</v>
       </c>
       <c r="C693" s="13" t="s">
-        <v>3742</v>
+        <v>3740</v>
       </c>
       <c r="D693" s="20" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="E693" s="24" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="694" spans="1:5">
@@ -38598,16 +38631,16 @@
         <v>693</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="C694" s="13" t="s">
-        <v>3744</v>
+        <v>3742</v>
       </c>
       <c r="D694" s="20" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="E694" s="24" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -38615,16 +38648,16 @@
         <v>694</v>
       </c>
       <c r="B695" s="3" t="s">
-        <v>3745</v>
+        <v>3743</v>
       </c>
       <c r="C695" s="13" t="s">
-        <v>3746</v>
+        <v>3744</v>
       </c>
       <c r="D695" s="20" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="E695" s="24" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="696" spans="1:5">
@@ -38632,16 +38665,16 @@
         <v>695</v>
       </c>
       <c r="B696" s="3" t="s">
-        <v>3747</v>
+        <v>3745</v>
       </c>
       <c r="C696" s="13" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="D696" s="20" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="E696" s="24" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="697" spans="1:5">
@@ -38649,16 +38682,16 @@
         <v>696</v>
       </c>
       <c r="B697" s="3" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C697" s="13" t="s">
-        <v>3961</v>
+        <v>3748</v>
       </c>
       <c r="D697" s="20" t="s">
-        <v>3964</v>
+        <v>3804</v>
       </c>
       <c r="E697" s="24" t="s">
-        <v>3964</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="698" spans="1:5">
@@ -38666,16 +38699,16 @@
         <v>697</v>
       </c>
       <c r="B698" s="3" t="s">
-        <v>3959</v>
+        <v>3749</v>
       </c>
       <c r="C698" s="13" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="D698" s="20" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="E698" s="24" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="699" spans="1:5">
@@ -38683,16 +38716,16 @@
         <v>698</v>
       </c>
       <c r="B699" s="3" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="C699" s="13" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="D699" s="20" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="E699" s="24" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="700" spans="1:5">
@@ -38700,16 +38733,16 @@
         <v>699</v>
       </c>
       <c r="B700" s="3" t="s">
-        <v>3750</v>
+        <v>3960</v>
       </c>
       <c r="C700" s="13" t="s">
-        <v>3751</v>
+        <v>3963</v>
       </c>
       <c r="D700" s="20" t="s">
-        <v>3805</v>
+        <v>3966</v>
       </c>
       <c r="E700" s="24" t="s">
-        <v>3805</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="701" spans="1:5">
@@ -38717,16 +38750,16 @@
         <v>700</v>
       </c>
       <c r="B701" s="3" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
       <c r="C701" s="13" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="D701" s="20" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="E701" s="24" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="702" spans="1:5">
@@ -38734,16 +38767,16 @@
         <v>701</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>3754</v>
+        <v>3752</v>
       </c>
       <c r="C702" s="13" t="s">
-        <v>3755</v>
+        <v>3753</v>
       </c>
       <c r="D702" s="20" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="E702" s="24" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="703" spans="1:5">
@@ -38751,16 +38784,16 @@
         <v>702</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>3756</v>
+        <v>3754</v>
       </c>
       <c r="C703" s="13" t="s">
-        <v>3757</v>
+        <v>3755</v>
       </c>
       <c r="D703" s="20" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="E703" s="24" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="704" spans="1:5">
@@ -38768,16 +38801,16 @@
         <v>703</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>3758</v>
+        <v>3756</v>
       </c>
       <c r="C704" s="13" t="s">
-        <v>3759</v>
+        <v>3757</v>
       </c>
       <c r="D704" s="20" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="E704" s="24" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="705" spans="1:5">
@@ -38785,16 +38818,16 @@
         <v>704</v>
       </c>
       <c r="B705" s="3" t="s">
-        <v>3760</v>
+        <v>3758</v>
       </c>
       <c r="C705" s="13" t="s">
-        <v>3761</v>
+        <v>3759</v>
       </c>
       <c r="D705" s="20" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="E705" s="24" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="706" spans="1:5">
@@ -38802,16 +38835,16 @@
         <v>705</v>
       </c>
       <c r="B706" s="3" t="s">
-        <v>3762</v>
+        <v>3760</v>
       </c>
       <c r="C706" s="13" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
       <c r="D706" s="20" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="E706" s="24" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="707" spans="1:5">
@@ -38819,16 +38852,16 @@
         <v>706</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
       <c r="C707" s="13" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
       <c r="D707" s="20" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="E707" s="24" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="708" spans="1:5">
@@ -38836,16 +38869,16 @@
         <v>707</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
       <c r="C708" s="13" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
       <c r="D708" s="20" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="E708" s="24" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="709" spans="1:5">
@@ -38853,16 +38886,16 @@
         <v>708</v>
       </c>
       <c r="B709" s="3" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
       <c r="C709" s="13" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
       <c r="D709" s="20" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="E709" s="24" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="710" spans="1:5">
@@ -38870,16 +38903,16 @@
         <v>709</v>
       </c>
       <c r="B710" s="3" t="s">
-        <v>4015</v>
+        <v>3768</v>
       </c>
       <c r="C710" s="13" t="s">
-        <v>4016</v>
+        <v>3769</v>
       </c>
       <c r="D710" s="20" t="s">
-        <v>4017</v>
+        <v>3814</v>
       </c>
       <c r="E710" s="24" t="s">
-        <v>4017</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="711" spans="1:5">
@@ -38887,16 +38920,16 @@
         <v>710</v>
       </c>
       <c r="B711" s="3" t="s">
-        <v>3770</v>
+        <v>4015</v>
       </c>
       <c r="C711" s="13" t="s">
-        <v>3771</v>
+        <v>4016</v>
       </c>
       <c r="D711" s="20" t="s">
-        <v>3815</v>
+        <v>4017</v>
       </c>
       <c r="E711" s="24" t="s">
-        <v>3815</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="712" spans="1:5">
@@ -38904,16 +38937,16 @@
         <v>711</v>
       </c>
       <c r="B712" s="3" t="s">
-        <v>3772</v>
+        <v>3770</v>
       </c>
       <c r="C712" s="13" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
       <c r="D712" s="20" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="E712" s="24" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="713" spans="1:5">
@@ -38921,16 +38954,16 @@
         <v>712</v>
       </c>
       <c r="B713" s="3" t="s">
-        <v>3774</v>
+        <v>3772</v>
       </c>
       <c r="C713" s="13" t="s">
-        <v>3775</v>
+        <v>3773</v>
       </c>
       <c r="D713" s="20" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="E713" s="24" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="714" spans="1:5">
@@ -38938,16 +38971,16 @@
         <v>713</v>
       </c>
       <c r="B714" s="3" t="s">
-        <v>3776</v>
+        <v>3774</v>
       </c>
       <c r="C714" s="13" t="s">
-        <v>3777</v>
+        <v>3775</v>
       </c>
       <c r="D714" s="20" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="E714" s="24" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="715" spans="1:5">
@@ -38955,16 +38988,16 @@
         <v>714</v>
       </c>
       <c r="B715" s="3" t="s">
-        <v>3778</v>
+        <v>3776</v>
       </c>
       <c r="C715" s="13" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
       <c r="D715" s="20" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="E715" s="24" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="716" spans="1:5">
@@ -38972,16 +39005,16 @@
         <v>715</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
       <c r="C716" s="13" t="s">
-        <v>3870</v>
+        <v>3779</v>
       </c>
       <c r="D716" s="20" t="s">
-        <v>3873</v>
+        <v>3819</v>
       </c>
       <c r="E716" s="24" t="s">
-        <v>3873</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="717" spans="1:5">
@@ -38989,16 +39022,16 @@
         <v>716</v>
       </c>
       <c r="B717" s="3" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="C717" s="13" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="D717" s="20" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="E717" s="24" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="718" spans="1:5">
@@ -39006,16 +39039,16 @@
         <v>717</v>
       </c>
       <c r="B718" s="3" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="C718" s="13" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="D718" s="20" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="E718" s="24" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="719" spans="1:5">
@@ -39023,16 +39056,16 @@
         <v>718</v>
       </c>
       <c r="B719" s="3" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="C719" s="13" t="s">
-        <v>3784</v>
+        <v>3872</v>
       </c>
       <c r="D719" s="20" t="s">
-        <v>3820</v>
+        <v>3875</v>
       </c>
       <c r="E719" s="24" t="s">
-        <v>3820</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="720" spans="1:5">
@@ -39040,16 +39073,16 @@
         <v>719</v>
       </c>
       <c r="B720" s="3" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
       <c r="C720" s="13" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
       <c r="D720" s="20" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="E720" s="24" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="721" spans="1:5">
@@ -39057,16 +39090,16 @@
         <v>720</v>
       </c>
       <c r="B721" s="3" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
       <c r="C721" s="13" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
       <c r="D721" s="20" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="E721" s="24" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="722" spans="1:5">
@@ -39074,16 +39107,16 @@
         <v>721</v>
       </c>
       <c r="B722" s="3" t="s">
-        <v>3789</v>
+        <v>3787</v>
       </c>
       <c r="C722" s="13" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
       <c r="D722" s="20" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="E722" s="24" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="723" spans="1:5">
@@ -39091,16 +39124,16 @@
         <v>722</v>
       </c>
       <c r="B723" s="3" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
       <c r="C723" s="13" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="D723" s="20" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="E723" s="24" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="724" spans="1:5">
@@ -39108,16 +39141,16 @@
         <v>723</v>
       </c>
       <c r="B724" s="3" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
       <c r="C724" s="13" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
       <c r="D724" s="20" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="E724" s="24" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="725" spans="1:5">
@@ -39125,16 +39158,16 @@
         <v>724</v>
       </c>
       <c r="B725" s="3" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
       <c r="C725" s="13" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="D725" s="20" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="E725" s="24" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -39142,16 +39175,16 @@
         <v>725</v>
       </c>
       <c r="B726" s="3" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
       <c r="C726" s="13" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
       <c r="D726" s="20" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="E726" s="24" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="727" spans="1:5">
@@ -39159,16 +39192,16 @@
         <v>726</v>
       </c>
       <c r="B727" s="3" t="s">
-        <v>3828</v>
+        <v>3797</v>
       </c>
       <c r="C727" s="13" t="s">
-        <v>3829</v>
+        <v>3798</v>
       </c>
       <c r="D727" s="20" t="s">
-        <v>3853</v>
+        <v>3827</v>
       </c>
       <c r="E727" s="24" t="s">
-        <v>3853</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="728" spans="1:5">
@@ -39176,16 +39209,16 @@
         <v>727</v>
       </c>
       <c r="B728" s="3" t="s">
-        <v>3830</v>
+        <v>3828</v>
       </c>
       <c r="C728" s="13" t="s">
-        <v>3831</v>
+        <v>3829</v>
       </c>
       <c r="D728" s="20" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="E728" s="24" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="729" spans="1:5">
@@ -39193,16 +39226,16 @@
         <v>728</v>
       </c>
       <c r="B729" s="3" t="s">
-        <v>3832</v>
+        <v>3830</v>
       </c>
       <c r="C729" s="13" t="s">
-        <v>3833</v>
+        <v>3831</v>
       </c>
       <c r="D729" s="20" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="E729" s="24" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -39210,16 +39243,16 @@
         <v>729</v>
       </c>
       <c r="B730" s="3" t="s">
-        <v>3834</v>
+        <v>3832</v>
       </c>
       <c r="C730" s="13" t="s">
-        <v>3141</v>
+        <v>3833</v>
       </c>
       <c r="D730" s="20" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="E730" s="24" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="731" spans="1:5">
@@ -39227,16 +39260,16 @@
         <v>730</v>
       </c>
       <c r="B731" s="3" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="C731" s="13" t="s">
-        <v>3836</v>
+        <v>3141</v>
       </c>
       <c r="D731" s="20" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="E731" s="24" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="732" spans="1:5">
@@ -39244,16 +39277,16 @@
         <v>731</v>
       </c>
       <c r="B732" s="3" t="s">
-        <v>3837</v>
+        <v>3835</v>
       </c>
       <c r="C732" s="13" t="s">
-        <v>3838</v>
+        <v>3836</v>
       </c>
       <c r="D732" s="20" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="E732" s="24" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="733" spans="1:5">
@@ -39261,16 +39294,16 @@
         <v>732</v>
       </c>
       <c r="B733" s="3" t="s">
-        <v>3839</v>
+        <v>3837</v>
       </c>
       <c r="C733" s="13" t="s">
-        <v>3840</v>
+        <v>3838</v>
       </c>
       <c r="D733" s="20" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="E733" s="24" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="734" spans="1:5">
@@ -39278,16 +39311,16 @@
         <v>733</v>
       </c>
       <c r="B734" s="3" t="s">
-        <v>3841</v>
+        <v>3839</v>
       </c>
       <c r="C734" s="13" t="s">
-        <v>3842</v>
+        <v>3840</v>
       </c>
       <c r="D734" s="20" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="E734" s="24" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -39295,16 +39328,16 @@
         <v>734</v>
       </c>
       <c r="B735" s="3" t="s">
-        <v>3843</v>
+        <v>3841</v>
       </c>
       <c r="C735" s="13" t="s">
-        <v>3844</v>
+        <v>3842</v>
       </c>
       <c r="D735" s="20" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="E735" s="24" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="736" spans="1:5">
@@ -39312,16 +39345,16 @@
         <v>735</v>
       </c>
       <c r="B736" s="3" t="s">
-        <v>3845</v>
+        <v>3843</v>
       </c>
       <c r="C736" s="13" t="s">
-        <v>3846</v>
+        <v>3844</v>
       </c>
       <c r="D736" s="20" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="E736" s="24" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="737" spans="1:5">
@@ -39329,16 +39362,16 @@
         <v>736</v>
       </c>
       <c r="B737" s="3" t="s">
-        <v>3847</v>
+        <v>3845</v>
       </c>
       <c r="C737" s="13" t="s">
-        <v>3848</v>
+        <v>3846</v>
       </c>
       <c r="D737" s="20" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="E737" s="24" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -39346,16 +39379,16 @@
         <v>737</v>
       </c>
       <c r="B738" s="3" t="s">
-        <v>3849</v>
+        <v>3847</v>
       </c>
       <c r="C738" s="13" t="s">
-        <v>3850</v>
+        <v>3848</v>
       </c>
       <c r="D738" s="20" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="E738" s="24" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="739" spans="1:5">
@@ -39363,16 +39396,16 @@
         <v>738</v>
       </c>
       <c r="B739" s="3" t="s">
-        <v>3851</v>
+        <v>3849</v>
       </c>
       <c r="C739" s="13" t="s">
-        <v>3852</v>
+        <v>3850</v>
       </c>
       <c r="D739" s="20" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="E739" s="24" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="740" spans="1:5">
@@ -39380,16 +39413,16 @@
         <v>739</v>
       </c>
       <c r="B740" s="3" t="s">
-        <v>3735</v>
+        <v>3851</v>
       </c>
       <c r="C740" s="13" t="s">
-        <v>3877</v>
+        <v>3852</v>
       </c>
       <c r="D740" s="20" t="s">
-        <v>3878</v>
+        <v>3865</v>
       </c>
       <c r="E740" s="24" t="s">
-        <v>3878</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="741" spans="1:5">
@@ -39397,16 +39430,16 @@
         <v>740</v>
       </c>
       <c r="B741" s="3" t="s">
-        <v>3879</v>
+        <v>3735</v>
       </c>
       <c r="C741" s="13" t="s">
-        <v>3880</v>
+        <v>3877</v>
       </c>
       <c r="D741" s="20" t="s">
-        <v>3883</v>
+        <v>3878</v>
       </c>
       <c r="E741" s="24" t="s">
-        <v>3883</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="742" spans="1:5">
@@ -39414,16 +39447,16 @@
         <v>741</v>
       </c>
       <c r="B742" s="3" t="s">
-        <v>3881</v>
+        <v>3879</v>
       </c>
       <c r="C742" s="13" t="s">
-        <v>3882</v>
+        <v>3880</v>
       </c>
       <c r="D742" s="20" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="E742" s="24" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="743" spans="1:5">
@@ -39431,16 +39464,16 @@
         <v>742</v>
       </c>
       <c r="B743" s="3" t="s">
-        <v>3885</v>
+        <v>3881</v>
       </c>
       <c r="C743" s="13" t="s">
-        <v>1099</v>
+        <v>3882</v>
       </c>
       <c r="D743" s="20" t="s">
-        <v>3242</v>
+        <v>3884</v>
       </c>
       <c r="E743" s="24" t="s">
-        <v>3242</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="744" spans="1:5">
@@ -39448,16 +39481,16 @@
         <v>743</v>
       </c>
       <c r="B744" s="3" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="C744" s="13" t="s">
-        <v>3887</v>
+        <v>1099</v>
       </c>
       <c r="D744" s="20" t="s">
-        <v>3900</v>
+        <v>3242</v>
       </c>
       <c r="E744" s="24" t="s">
-        <v>3900</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="745" spans="1:5">
@@ -39465,16 +39498,16 @@
         <v>744</v>
       </c>
       <c r="B745" s="3" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
       <c r="C745" s="13" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
       <c r="D745" s="20" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="E745" s="24" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="746" spans="1:5">
@@ -39482,16 +39515,16 @@
         <v>745</v>
       </c>
       <c r="B746" s="3" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
       <c r="C746" s="13" t="s">
-        <v>3891</v>
+        <v>3889</v>
       </c>
       <c r="D746" s="20" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="E746" s="24" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="747" spans="1:5">
@@ -39499,16 +39532,16 @@
         <v>746</v>
       </c>
       <c r="B747" s="3" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
       <c r="C747" s="13" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
       <c r="D747" s="20" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="E747" s="24" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="748" spans="1:5">
@@ -39516,16 +39549,16 @@
         <v>747</v>
       </c>
       <c r="B748" s="3" t="s">
-        <v>3894</v>
+        <v>3892</v>
       </c>
       <c r="C748" s="13" t="s">
-        <v>3895</v>
+        <v>3893</v>
       </c>
       <c r="D748" s="20" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="E748" s="24" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="749" spans="1:5">
@@ -39533,16 +39566,16 @@
         <v>748</v>
       </c>
       <c r="B749" s="3" t="s">
-        <v>3896</v>
+        <v>3894</v>
       </c>
       <c r="C749" s="13" t="s">
-        <v>3897</v>
+        <v>3895</v>
       </c>
       <c r="D749" s="20" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="E749" s="24" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="750" spans="1:5">
@@ -39550,16 +39583,16 @@
         <v>749</v>
       </c>
       <c r="B750" s="3" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
       <c r="C750" s="13" t="s">
-        <v>3899</v>
+        <v>3897</v>
       </c>
       <c r="D750" s="20" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="E750" s="24" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="751" spans="1:5">
@@ -39567,16 +39600,16 @@
         <v>750</v>
       </c>
       <c r="B751" s="3" t="s">
-        <v>3910</v>
+        <v>3898</v>
       </c>
       <c r="C751" s="13" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D751" s="13" t="s">
-        <v>3908</v>
-      </c>
-      <c r="E751" s="46" t="s">
-        <v>3908</v>
+        <v>3899</v>
+      </c>
+      <c r="D751" s="20" t="s">
+        <v>3906</v>
+      </c>
+      <c r="E751" s="24" t="s">
+        <v>3906</v>
       </c>
     </row>
     <row r="752" spans="1:5">
@@ -39584,16 +39617,16 @@
         <v>751</v>
       </c>
       <c r="B752" s="3" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="C752" s="13" t="s">
-        <v>3907</v>
+        <v>1958</v>
       </c>
       <c r="D752" s="13" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="E752" s="46" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="753" spans="1:5">
@@ -39601,16 +39634,16 @@
         <v>752</v>
       </c>
       <c r="B753" s="3" t="s">
-        <v>3915</v>
+        <v>3911</v>
       </c>
       <c r="C753" s="13" t="s">
-        <v>3916</v>
-      </c>
-      <c r="D753" s="20" t="s">
-        <v>3917</v>
-      </c>
-      <c r="E753" s="24" t="s">
-        <v>3917</v>
+        <v>3907</v>
+      </c>
+      <c r="D753" s="13" t="s">
+        <v>3909</v>
+      </c>
+      <c r="E753" s="46" t="s">
+        <v>3909</v>
       </c>
     </row>
     <row r="754" spans="1:5">
@@ -39618,16 +39651,16 @@
         <v>753</v>
       </c>
       <c r="B754" s="3" t="s">
-        <v>3923</v>
+        <v>3915</v>
       </c>
       <c r="C754" s="13" t="s">
-        <v>3924</v>
+        <v>3916</v>
       </c>
       <c r="D754" s="20" t="s">
-        <v>3925</v>
+        <v>3917</v>
       </c>
       <c r="E754" s="24" t="s">
-        <v>3925</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="755" spans="1:5">
@@ -39635,16 +39668,16 @@
         <v>754</v>
       </c>
       <c r="B755" s="3" t="s">
-        <v>3928</v>
+        <v>3923</v>
       </c>
       <c r="C755" s="13" t="s">
-        <v>3926</v>
+        <v>3924</v>
       </c>
       <c r="D755" s="20" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
       <c r="E755" s="24" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="756" spans="1:5">
@@ -39652,16 +39685,16 @@
         <v>755</v>
       </c>
       <c r="B756" s="3" t="s">
-        <v>3937</v>
+        <v>3928</v>
       </c>
       <c r="C756" s="13" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="D756" s="20" t="s">
-        <v>3930</v>
+        <v>3927</v>
       </c>
       <c r="E756" s="24" t="s">
-        <v>3930</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="757" spans="1:5">
@@ -39669,16 +39702,16 @@
         <v>756</v>
       </c>
       <c r="B757" s="3" t="s">
-        <v>3933</v>
+        <v>3937</v>
       </c>
       <c r="C757" s="13" t="s">
-        <v>3931</v>
+        <v>3929</v>
       </c>
       <c r="D757" s="20" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="E757" s="24" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="758" spans="1:5">
@@ -39686,16 +39719,16 @@
         <v>757</v>
       </c>
       <c r="B758" s="3" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="C758" s="13" t="s">
-        <v>3935</v>
+        <v>3931</v>
       </c>
       <c r="D758" s="20" t="s">
-        <v>3936</v>
+        <v>3932</v>
       </c>
       <c r="E758" s="24" t="s">
-        <v>3936</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="759" spans="1:5">
@@ -39703,16 +39736,16 @@
         <v>758</v>
       </c>
       <c r="B759" s="3" t="s">
-        <v>3942</v>
+        <v>3934</v>
       </c>
       <c r="C759" s="13" t="s">
-        <v>3940</v>
+        <v>3935</v>
       </c>
       <c r="D759" s="20" t="s">
-        <v>3941</v>
+        <v>3936</v>
       </c>
       <c r="E759" s="24" t="s">
-        <v>3941</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="760" spans="1:5">
@@ -39720,16 +39753,16 @@
         <v>759</v>
       </c>
       <c r="B760" s="3" t="s">
-        <v>3947</v>
+        <v>3942</v>
       </c>
       <c r="C760" s="13" t="s">
-        <v>3948</v>
+        <v>3940</v>
       </c>
       <c r="D760" s="20" t="s">
-        <v>3949</v>
+        <v>3941</v>
       </c>
       <c r="E760" s="24" t="s">
-        <v>3949</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="761" spans="1:5">
@@ -39737,16 +39770,16 @@
         <v>760</v>
       </c>
       <c r="B761" s="3" t="s">
-        <v>3950</v>
+        <v>3947</v>
       </c>
       <c r="C761" s="13" t="s">
-        <v>3951</v>
+        <v>3948</v>
       </c>
       <c r="D761" s="20" t="s">
-        <v>3952</v>
+        <v>3949</v>
       </c>
       <c r="E761" s="24" t="s">
-        <v>3952</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="762" spans="1:5">
@@ -39754,16 +39787,16 @@
         <v>761</v>
       </c>
       <c r="B762" s="3" t="s">
-        <v>3953</v>
+        <v>3950</v>
       </c>
       <c r="C762" s="13" t="s">
-        <v>3954</v>
+        <v>3951</v>
       </c>
       <c r="D762" s="20" t="s">
-        <v>3955</v>
+        <v>3952</v>
       </c>
       <c r="E762" s="24" t="s">
-        <v>3955</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="763" spans="1:5">
@@ -39771,16 +39804,16 @@
         <v>762</v>
       </c>
       <c r="B763" s="3" t="s">
-        <v>3956</v>
+        <v>3953</v>
       </c>
       <c r="C763" s="13" t="s">
-        <v>3957</v>
+        <v>3954</v>
       </c>
       <c r="D763" s="20" t="s">
-        <v>3958</v>
+        <v>3955</v>
       </c>
       <c r="E763" s="24" t="s">
-        <v>3958</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="764" spans="1:5">
@@ -39788,16 +39821,16 @@
         <v>763</v>
       </c>
       <c r="B764" s="3" t="s">
-        <v>3967</v>
+        <v>3956</v>
       </c>
       <c r="C764" s="13" t="s">
-        <v>3968</v>
+        <v>3957</v>
       </c>
       <c r="D764" s="20" t="s">
-        <v>3995</v>
+        <v>3958</v>
       </c>
       <c r="E764" s="24" t="s">
-        <v>3995</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="765" spans="1:5">
@@ -39805,16 +39838,16 @@
         <v>764</v>
       </c>
       <c r="B765" s="3" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
       <c r="C765" s="13" t="s">
-        <v>3970</v>
+        <v>3968</v>
       </c>
       <c r="D765" s="20" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="E765" s="24" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="766" spans="1:5">
@@ -39822,16 +39855,16 @@
         <v>765</v>
       </c>
       <c r="B766" s="3" t="s">
-        <v>3971</v>
+        <v>3969</v>
       </c>
       <c r="C766" s="13" t="s">
-        <v>3972</v>
+        <v>3970</v>
       </c>
       <c r="D766" s="20" t="s">
-        <v>3984</v>
+        <v>3996</v>
       </c>
       <c r="E766" s="24" t="s">
-        <v>3984</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="767" spans="1:5">
@@ -39839,16 +39872,16 @@
         <v>766</v>
       </c>
       <c r="B767" s="3" t="s">
-        <v>3973</v>
+        <v>3971</v>
       </c>
       <c r="C767" s="13" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
       <c r="D767" s="20" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="E767" s="24" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="768" spans="1:5">
@@ -39856,16 +39889,16 @@
         <v>767</v>
       </c>
       <c r="B768" s="3" t="s">
-        <v>3975</v>
+        <v>3973</v>
       </c>
       <c r="C768" s="13" t="s">
-        <v>3976</v>
+        <v>3974</v>
       </c>
       <c r="D768" s="20" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="E768" s="24" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="769" spans="1:5">
@@ -39873,16 +39906,16 @@
         <v>768</v>
       </c>
       <c r="B769" s="3" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
       <c r="C769" s="13" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
       <c r="D769" s="20" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="E769" s="24" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="770" spans="1:5">
@@ -39890,16 +39923,16 @@
         <v>769</v>
       </c>
       <c r="B770" s="3" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
       <c r="C770" s="13" t="s">
-        <v>3980</v>
+        <v>3978</v>
       </c>
       <c r="D770" s="20" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="E770" s="24" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="771" spans="1:5">
@@ -39907,16 +39940,16 @@
         <v>770</v>
       </c>
       <c r="B771" s="3" t="s">
-        <v>3998</v>
+        <v>3979</v>
       </c>
       <c r="C771" s="13" t="s">
-        <v>4013</v>
+        <v>3980</v>
       </c>
       <c r="D771" s="20" t="s">
-        <v>4014</v>
+        <v>3988</v>
       </c>
       <c r="E771" s="24" t="s">
-        <v>4014</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="772" spans="1:5">
@@ -39924,16 +39957,16 @@
         <v>771</v>
       </c>
       <c r="B772" s="3" t="s">
-        <v>3981</v>
+        <v>3998</v>
       </c>
       <c r="C772" s="13" t="s">
-        <v>3982</v>
+        <v>4013</v>
       </c>
       <c r="D772" s="20" t="s">
-        <v>3989</v>
+        <v>4014</v>
       </c>
       <c r="E772" s="24" t="s">
-        <v>3989</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="773" spans="1:5">
@@ -39941,16 +39974,16 @@
         <v>772</v>
       </c>
       <c r="B773" s="3" t="s">
-        <v>3983</v>
+        <v>3981</v>
       </c>
       <c r="C773" s="13" t="s">
-        <v>3990</v>
+        <v>3982</v>
       </c>
       <c r="D773" s="20" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
       <c r="E773" s="24" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="774" spans="1:5">
@@ -39958,16 +39991,16 @@
         <v>773</v>
       </c>
       <c r="B774" s="3" t="s">
-        <v>3992</v>
+        <v>3983</v>
       </c>
       <c r="C774" s="13" t="s">
-        <v>3993</v>
+        <v>3990</v>
       </c>
       <c r="D774" s="20" t="s">
-        <v>3994</v>
+        <v>3991</v>
       </c>
       <c r="E774" s="24" t="s">
-        <v>3994</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="775" spans="1:5">
@@ -39975,16 +40008,16 @@
         <v>774</v>
       </c>
       <c r="B775" s="3" t="s">
-        <v>4001</v>
+        <v>3992</v>
       </c>
       <c r="C775" s="13" t="s">
-        <v>3999</v>
+        <v>3993</v>
       </c>
       <c r="D775" s="20" t="s">
-        <v>4000</v>
+        <v>3994</v>
       </c>
       <c r="E775" s="24" t="s">
-        <v>4000</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="776" spans="1:5">
@@ -39992,16 +40025,16 @@
         <v>775</v>
       </c>
       <c r="B776" s="3" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C776" s="13" t="s">
-        <v>4003</v>
+        <v>3999</v>
       </c>
       <c r="D776" s="20" t="s">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="E776" s="24" t="s">
-        <v>4005</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="777" spans="1:5">
@@ -40009,16 +40042,16 @@
         <v>776</v>
       </c>
       <c r="B777" s="3" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="C777" s="13" t="s">
-        <v>4006</v>
+        <v>4003</v>
       </c>
       <c r="D777" s="20" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="E777" s="24" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="778" spans="1:5">
@@ -40026,16 +40059,16 @@
         <v>777</v>
       </c>
       <c r="B778" s="3" t="s">
-        <v>4010</v>
+        <v>4004</v>
       </c>
       <c r="C778" s="13" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="D778" s="20" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="E778" s="24" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="779" spans="1:5">
@@ -40043,16 +40076,16 @@
         <v>778</v>
       </c>
       <c r="B779" s="3" t="s">
-        <v>4030</v>
+        <v>4010</v>
       </c>
       <c r="C779" s="13" t="s">
-        <v>4031</v>
+        <v>4008</v>
       </c>
       <c r="D779" s="20" t="s">
-        <v>4032</v>
+        <v>4009</v>
       </c>
       <c r="E779" s="24" t="s">
-        <v>4032</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="780" spans="1:5">
@@ -40060,16 +40093,16 @@
         <v>779</v>
       </c>
       <c r="B780" s="3" t="s">
-        <v>4033</v>
+        <v>4030</v>
       </c>
       <c r="C780" s="13" t="s">
-        <v>4034</v>
+        <v>4031</v>
       </c>
       <c r="D780" s="20" t="s">
-        <v>4035</v>
+        <v>4032</v>
       </c>
       <c r="E780" s="24" t="s">
-        <v>4035</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="781" spans="1:5">
@@ -40077,16 +40110,16 @@
         <v>780</v>
       </c>
       <c r="B781" s="3" t="s">
-        <v>4036</v>
+        <v>4033</v>
       </c>
       <c r="C781" s="13" t="s">
-        <v>4037</v>
+        <v>4034</v>
       </c>
       <c r="D781" s="20" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
       <c r="E781" s="24" t="s">
-        <v>4040</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="782" spans="1:5">
@@ -40094,16 +40127,16 @@
         <v>781</v>
       </c>
       <c r="B782" s="3" t="s">
-        <v>4038</v>
+        <v>4036</v>
       </c>
       <c r="C782" s="13" t="s">
-        <v>4039</v>
+        <v>4037</v>
       </c>
       <c r="D782" s="20" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="E782" s="24" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="783" spans="1:5">
@@ -40111,16 +40144,50 @@
         <v>782</v>
       </c>
       <c r="B783" s="3" t="s">
+        <v>4038</v>
+      </c>
+      <c r="C783" s="13" t="s">
+        <v>4039</v>
+      </c>
+      <c r="D783" s="20" t="s">
+        <v>4041</v>
+      </c>
+      <c r="E783" s="24" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5">
+      <c r="A784" s="11">
+        <v>783</v>
+      </c>
+      <c r="B784" s="3" t="s">
         <v>4594</v>
       </c>
-      <c r="C783" s="13" t="s">
+      <c r="C784" s="13" t="s">
         <v>4595</v>
       </c>
-      <c r="D783" s="20" t="s">
+      <c r="D784" s="20" t="s">
         <v>4596</v>
       </c>
-      <c r="E783" s="24" t="s">
+      <c r="E784" s="24" t="s">
         <v>4596</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5">
+      <c r="A785" s="11">
+        <v>784</v>
+      </c>
+      <c r="B785" s="3" t="s">
+        <v>4605</v>
+      </c>
+      <c r="C785" s="13" t="s">
+        <v>4606</v>
+      </c>
+      <c r="D785" s="20" t="s">
+        <v>4607</v>
+      </c>
+      <c r="E785" s="24" t="s">
+        <v>4607</v>
       </c>
     </row>
   </sheetData>
